--- a/manuscript_material/on_demand/Source_Data_OD_Fig7.xlsx
+++ b/manuscript_material/on_demand/Source_Data_OD_Fig7.xlsx
@@ -758,25 +758,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" t="n">
-        <v>87.06999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="F8" t="n">
-        <v>82.86</v>
+        <v>86.11</v>
       </c>
       <c r="G8" t="n">
-        <v>4.22</v>
+        <v>-0.61</v>
       </c>
       <c r="H8" t="n">
-        <v>7.89</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.88</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>25</v>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -811,19 +811,19 @@
         <v>91.20999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>95.08</v>
+        <v>96.72</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.87</v>
+        <v>-5.51</v>
       </c>
       <c r="H9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.26</v>
+        <v>-11.11</v>
       </c>
       <c r="J9" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -855,10 +855,10 @@
         <v>82.39</v>
       </c>
       <c r="F10" t="n">
-        <v>88.59999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.21</v>
+        <v>-7.09</v>
       </c>
       <c r="H10" t="n">
         <v>-4.65</v>
@@ -890,28 +890,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E11" t="n">
-        <v>83.08</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>85.88</v>
+        <v>85.63</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.81</v>
+        <v>-2.17</v>
       </c>
       <c r="H11" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="I11" t="n">
-        <v>-8.140000000000001</v>
+        <v>-9.09</v>
       </c>
       <c r="J11" t="n">
-        <v>14.1</v>
+        <v>15.12</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -934,28 +934,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D12" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E12" t="n">
-        <v>86.63</v>
+        <v>86.17</v>
       </c>
       <c r="F12" t="n">
-        <v>87.89</v>
+        <v>88.62</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.26</v>
+        <v>-2.45</v>
       </c>
       <c r="H12" t="n">
         <v>1.9</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.83</v>
+        <v>-5.01</v>
       </c>
       <c r="J12" t="n">
-        <v>8.369999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D6" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1177,10 +1177,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H6" t="n">
-        <v>87.89</v>
+        <v>88.62</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -1196,22 +1196,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>567</v>
+        <v>611</v>
       </c>
       <c r="D7" t="n">
-        <v>504</v>
+        <v>536</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>88.89</v>
+        <v>87.73</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -1227,22 +1227,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>240</v>
+        <v>198</v>
       </c>
       <c r="D8" t="n">
-        <v>196</v>
+        <v>162</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>81.67</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -1590,16 +1590,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>13.89</v>
+        <v>12.5</v>
       </c>
       <c r="F9" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1624,16 +1624,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E10" t="n">
-        <v>32.41</v>
+        <v>39.29</v>
       </c>
       <c r="F10" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G10" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1658,16 +1658,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2.78</v>
+        <v>1.79</v>
       </c>
       <c r="F11" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1692,13 +1692,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7</v>
+        <v>5.36</v>
       </c>
       <c r="F12" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1726,16 +1726,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>20.37</v>
+        <v>16.96</v>
       </c>
       <c r="F13" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1760,13 +1760,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>4.63</v>
+        <v>3.57</v>
       </c>
       <c r="F14" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -1794,13 +1794,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E15" t="n">
-        <v>22.22</v>
+        <v>20.54</v>
       </c>
       <c r="F15" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:K135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3353,17 +3353,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>chip-pioneer-q1</t>
+          <t>atac-tn5-shift-q1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r1</t>
+          <t>galaxy_codex_gpt_5_5_r3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3388,17 +3388,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>82; 89</t>
+          <t>95; 98; 100; 101</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>72; 77; 82</t>
+          <t>36; 70; 92; 100</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>pioneer-full-count-v1 UDT computed a closed-versus-open log2 index over all fragments normalized to input, without defining ChIP-enriched sites; background dominated and TF3 won by a small margin.</t>
+          <t>De novo scorer UDT ranked 2;-1 first (L70), but the agent overrode it with a HINT 8-mer bias-table scorer UDT whose re-offset k-mer convention (L95, L98) ranked 6;-5 first (L100); submitted directly (L101).</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r2</t>
+          <t>galaxy_codex_gpt_5_6_luna_r1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>232; 249</t>
+          <t>82; 89</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>229; 232</t>
+          <t>72; 77; 82</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>bj-chip-pioneer-score UDT counted all fragments inside/outside DNase peaks relative to input, never restricting to ChIP-enriched regions; sort1 ranking of its near-tied closed enrichment (0.948-0.975) picked TF1.</t>
+          <t>pioneer-full-count-v1 UDT computed a closed-versus-open log2 index over all fragments normalized to input, without defining ChIP-enriched sites; background dominated and TF3 won by a small margin.</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r3</t>
+          <t>galaxy_codex_gpt_5_6_luna_r2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3502,17 +3502,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>93; 94</t>
+          <t>232; 249</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>78; 85; 93</t>
+          <t>229; 232</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>pioneer-analysis-v1 UDT scored bulk fragment accessible/closed fractions with input-normalized closed log2 enrichment over all fragments; background-dominated metric made TF1 top. Method error in UDT code.</t>
+          <t>bj-chip-pioneer-score UDT counted all fragments inside/outside DNase peaks relative to input, never restricting to ChIP-enriched regions; sort1 ranking of its near-tied closed enrichment (0.948-0.975) picked TF1.</t>
         </is>
       </c>
     </row>
@@ -3524,17 +3524,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>conservation-lookup-q1</t>
+          <t>chip-pioneer-q1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r1</t>
+          <t>galaxy_codex_gpt_5_6_luna_r3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3559,17 +3559,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>93; 94</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>33; 70; 135; 156</t>
+          <t>78; 85; 93</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Final UDT shh-final-distance-analysis-v2 cut each Ensembl ortholog from its own annotated start codon (309 nt, +9); its diagnostics' cactus_distance equals the reference, but the script emitted own-start distances.</t>
+          <t>pioneer-analysis-v1 UDT scored bulk fragment accessible/closed fractions with input-normalized closed log2 enrichment over all fragments; background-dominated metric made TF1 top. Method error in UDT code.</t>
         </is>
       </c>
     </row>
@@ -3586,17 +3586,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>galaxy_codex_deepseek_v4_pro_0813_r3</t>
+          <t>galaxy_codex_gpt_5_5_r1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (Codex)</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BEFORE_UDT</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3616,17 +3616,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>262; 360</t>
+          <t>156</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>266; 659</t>
+          <t>33; 70; 135; 156</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Segments were built locally from canonical transcripts including the upstream ATGGGCGAG extension (309 nt; L262) and staged as segments_all.fasta; lev_dist_v1 correctly computed Levenshtein on those wrong inputs.</t>
+          <t>Final UDT shh-final-distance-analysis-v2 cut each Ensembl ortholog from its own annotated start codon (309 nt, +9); its diagnostics' cactus_distance equals the reference, but the script emitted own-start distances.</t>
         </is>
       </c>
     </row>
@@ -3643,47 +3643,47 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r1</t>
+          <t>galaxy_codex_deepseek_v4_pro_0813_r3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UDT_FAILED_NOT_DECISIVE</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>galaxy_wrapper</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>117; 316; 324; 459</t>
+          <t>224; 294; 302</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>149; 168</t>
+          <t>278; 282; 302</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Extraction UDT failed pre-render; its staged script cut each ortholog from its own start codon (L147), exactly as the Galaxy extractseq fallback did. The segment definition, not the UDT failure, produced the wrong distances.</t>
+          <t>Final UDT (L302) cut chimp/macaque/beluga from their own annotated ATG (309 nt, +9 'MGE' artefact) and, after local check L294, extended Indri/Semnopithecus segments 9 nt upstream, turning correct 20,5 (UDT L282) into 29,14.</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r2</t>
+          <t>galaxy_codex_gpt_5_6_luna_r1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>444; 1080; 1135</t>
+          <t>117; 316; 324; 459</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>136; 149; 151; 153; 169; 171; 173; 177; 209; 219; 221; 223; 231</t>
+          <t>149; 168</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Transcript-diagnostic UDT (answer input) failed pre-render (L136); agent switched to ordinary Galaxy tools keeping the same canonical-segment definition (L326). The +9 own-start-codon segments are route-independent, as in Luna r1's UDT script.</t>
+          <t>Extraction UDT failed pre-render; its staged script cut each ortholog from its own start codon (L147), exactly as the Galaxy extractseq fallback did. The segment definition, not the UDT failure, produced the wrong distances.</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r3</t>
+          <t>galaxy_codex_gpt_5_6_luna_r2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3767,37 +3767,37 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UDT_FAILED_NOT_DECISIVE</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>galaxy_wrapper</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>361; 578; 621; 624</t>
+          <t>213; 328</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>87; 110; 114; 168; 170; 172; 174; 254; 262</t>
+          <t>90; 93; 213; 266; 307; 324; 328</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Transcript-diagnostic UDT (answer input) failed pre-render (L87); vsearch/mothur fallback used canonical segments from each ortholog's own start codon (L325), the same definition as Luna r1's UDT script. Failure not decisive.</t>
+          <t>UDT shh-segment-distance-v1 (L213) extracted each ortholog 'start_codon_to_exon1_end' from its own annotated start, giving 309-nt chimp/macaque/beluga segments (+9 upstream codons); final UDT (L328) reported 9,16,0,20,5,24,35. Indri and langur values were correct.</t>
         </is>
       </c>
     </row>
@@ -3809,22 +3809,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>contaminated-rna-q1</t>
+          <t>conservation-lookup-q1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r3</t>
+          <t>galaxy_codex_gpt_5_6_luna_r3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>NOT_ON_PATH</t>
+          <t>UDT_FAILED_NOT_DECISIVE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3844,17 +3844,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>131; 138; 141; 146</t>
+          <t>361; 578; 621; 624</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>90; 98</t>
+          <t>87; 110; 114; 168; 170; 172; 174; 254; 262</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Both k-mer panel UDTs were a side screen launched while Kraken2 jobs ran, and both failed before rendering. The answer came from the Kraken2 standard-16 wrapper (no cnidarians; EBV 195 reads) after core_nt returned empty outputs.</t>
+          <t>Transcript-diagnostic UDT (answer input) failed pre-render (L87); vsearch/mothur fallback used canonical segments from each ortholog's own start codon (L325), the same definition as Luna r1's UDT script. Failure not decisive.</t>
         </is>
       </c>
     </row>
@@ -3871,47 +3871,47 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r3</t>
+          <t>galaxy_codex_gpt_5_6_sol_r2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UDT_FAILED_NOT_DECISIVE</t>
+          <t>BEFORE_UDT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>galaxy_wrapper</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>45; 100; 162; 211; 223</t>
+          <t>505; 508; 534; 617</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>162; 171; 188; 191</t>
+          <t>376; 633; 638</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Competitive-mapping UDT failed at rendering; its reference inputs (human, mouse, Mesomycoplasma, Bacillus, Mycobacterium) already lacked chimp, chosen after core_nt timeout and primate-free Kraken2. minimap2 wrapper fallback used the same panel, answering mesomycoplasma.</t>
+          <t>Bowtie2 hg38 subtraction removed chimp reads and the genome panel lacked primates; rodent-score UDT faithfully compared mm10 vs rn6 BAMs of conserved background reads, yielding the marginal rat call (1,001 vs 960).</t>
         </is>
       </c>
     </row>
@@ -3923,52 +3923,52 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>contaminated-rna-q3</t>
+          <t>covid-patient-q1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_sol_r2</t>
+          <t>galaxy_codex_deepseek_v4_pro_0813_r3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>BEFORE_UDT</t>
+          <t>UDT_FAILED_NOT_DECISIVE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>answer_producing</t>
+          <t>failed_only</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>udt</t>
+          <t>galaxy_wrapper</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>505; 508; 534; 617</t>
+          <t>94; 166; 881; 884</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>376; 633; 638</t>
+          <t>94; 130; 132; 138</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Bowtie2 hg38 subtraction removed chimp reads and the genome panel lacked primates; rodent-score UDT faithfully compared mm10 vs rn6 BAMs of conserved background reads, yielding the marginal rat call (1,001 vs 960).</t>
+          <t>covid_donor_metrics.py (read at L581) computed only a per-donor ISG score; the UDT failed at rendering. Scanpy score_genes, datamash and filter wrappers applied the same ISG-only threshold, calling 23 donors healthy.</t>
         </is>
       </c>
     </row>
@@ -3985,27 +3985,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>galaxy_codex_deepseek_v4_pro_0813_r3</t>
+          <t>galaxy_codex_gpt_5_6_luna_r1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (Codex)</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UDT_FAILED_NOT_DECISIVE</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>galaxy_wrapper</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4015,17 +4015,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>94; 166; 881; 884</t>
+          <t>234; 239; 245</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>94; 130; 132; 138</t>
+          <t>89; 156; 167; 234; 239; 245</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>covid_donor_metrics.py (read at L581) computed only a per-donor ISG score; the UDT failed at rendering. Scanpy score_genes, datamash and filter wrappers applied the same ISG-only threshold, calling 23 donors healthy.</t>
+          <t>Final classification UDT v3 applied an interferon-only gap threshold, forced to at least six high donors, labelling 8 high-ISG donors COVID and 25 healthy; low-ISG COVID donors were missed.</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r1</t>
+          <t>galaxy_codex_gpt_5_6_luna_r3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4072,17 +4072,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>234; 239; 245</t>
+          <t>142; 143; 149</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>89; 156; 167; 234; 239; 245</t>
+          <t>120; 133; 142; 149</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Final classification UDT v3 applied an interferon-only gap threshold, forced to at least six high donors, labelling 8 high-ISG donors COVID and 25 healthy; low-ISG COVID donors were missed.</t>
+          <t>Diagnostic and confirmatory UDTs used the rule ISG mean at least 0.50 with half of cells above, calling only 8 donors COVID and the other 25 healthy. ISG-only method error in UDT code.</t>
         </is>
       </c>
     </row>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>covid-patient-q1</t>
+          <t>deg-simple-q2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r3</t>
+          <t>galaxy_codex_gpt_5_6_luna_r1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4124,22 +4124,22 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>142; 143; 149</t>
+          <t>388; 403; 405</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>120; 133; 142; 149</t>
+          <t>374; 388; 405</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Diagnostic and confirmatory UDTs used the rule ISG mean at least 0.50 with half of cells above, calling only 8 donors COVID and the other 25 healthy. ISG-only method error in UDT code.</t>
+          <t>UDT isoform-switch-diagnostic-v2 applied a post-hoc filter (isoform-fraction change &gt;=0.10 plus unadjusted Cuffdiff p&lt;0.05, all q~0.49) to noisy n=1 StringTie/Cuffdiff output, leaving only MS4A1; genes were never ranked by read-supported switches.</t>
         </is>
       </c>
     </row>
@@ -4151,22 +4151,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>deg-simple-q2</t>
+          <t>encode-atac-pipeline-q1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r1</t>
+          <t>galaxy_codex_gpt_5_5_r1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UDT_CODE</t>
+          <t>UDT_EXECUTION</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4186,17 +4186,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>388; 403; 405</t>
+          <t>134</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>374; 388; 405</t>
+          <t>108; 114; 131; 134</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>UDT isoform-switch-diagnostic-v2 applied a post-hoc filter (isoform-fraction change &gt;=0.10 plus unadjusted Cuffdiff p&lt;0.05, all q~0.49) to noisy n=1 StringTie/Cuffdiff output, leaving only MS4A1; genes were never ranked by read-supported switches.</t>
+          <t>Full ENCODE v2.2.3 run inside UDT encode-atac-223-q1-run-v4 received Galaxy-staged dataset_*.dat paths; extension-based adapter detection silently skipped trimming (5,000,000 reads, 75.4% mapped, NFR 0.098), yielding N_opt 13636.</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r1</t>
+          <t>galaxy_codex_gpt_5_5_r2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4243,17 +4243,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>180; 190</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>108; 114; 131; 134</t>
+          <t>100; 139; 159; 170; 190</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Full ENCODE v2.2.3 run inside UDT encode-atac-223-q1-run-v4 received Galaxy-staged dataset_*.dat paths; extension-based adapter detection silently skipped trimming (5,000,000 reads, 75.4% mapped, NFR 0.098), yielding N_opt 13636.</t>
+          <t>Final in-container ENCODE UDT (L190) passed Galaxy-localised dataset_*.dat FASTQ paths, disabling extension-based adapter autodetection; QC shows untrimmed signature (75.4% mapped, NFR 0.098), N_opt 13636. Suffix symlinks (L180) covered references only.</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r2</t>
+          <t>galaxy_codex_gpt_5_6_sol_r2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4285,32 +4285,32 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>local_shell</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>25; 50; 53; 109; 271</t>
+          <t>190</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>25; 33; 47; 50; 53; 75; 109</t>
+          <t>88; 107; 142; 190</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Even minimal UDT probes failed before command rendering, blocking the planned container pipeline. The local aarch64 fallback (MACS2 2.2.9.1, substituted tools) gave N_opt 28285, a route-determined result unlike the pinned container's.</t>
+          <t>Final UDT encode-atac-v223-q1-r4-py36 ran the full pipeline on Galaxy-staged dataset_*.dat FASTQ paths; extension-based adapter detection skipped trimming (5,000,000 reads, 75.4% mapped, NFR 0.098), producing N_opt 13636.</t>
         </is>
       </c>
     </row>
@@ -4327,12 +4327,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r3</t>
+          <t>galaxy_codex_gpt_5_6_sol_r3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4342,32 +4342,32 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>local_shell</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>24; 43; 56; 276</t>
+          <t>148</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>24; 33; 43; 56</t>
+          <t>89; 148</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>All four UDTs, even echo and the documented cat example, failed before command rendering. The local aarch64 fallback with non-pinned MACS2/IDR gave N_opt 28301, a route-determined result unlike the pinned container's.</t>
+          <t>UDT encode-atac-seq-pipeline-223-hg38-pe-v2 ran the full pipeline with Galaxy-staged extension-less input paths; adapter autodetection silently failed, and the untrimmed alignment (5,000,000 reads) gave N_opt 13636, reported directly.</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_sol_r2</t>
+          <t>galaxy_codex_deepseek_v4_pro_0813_r2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4414,17 +4414,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>286</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>88; 107; 142; 190</t>
+          <t>247; 264; 274; 286</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Final UDT encode-atac-v223-q1-r4-py36 ran the full pipeline on Galaxy-staged dataset_*.dat FASTQ paths; extension-based adapter detection skipped trimming (5,000,000 reads, 75.4% mapped, NFR 0.098), producing N_opt 13636.</t>
+          <t>UDT encode-atac-run-v4 ran the pipeline with Galaxy-bound dataset_*.dat FASTQ paths passed straight into the input JSON; extension-based adapter detection found nothing, so reads were untrimmed and N_opt was 13636.</t>
         </is>
       </c>
     </row>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_sol_r3</t>
+          <t>galaxy_codex_deepseek_v4_pro_0813_r3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>137; 294</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>89; 148</t>
+          <t>204; 216; 220; 230; 294</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>UDT encode-atac-seq-pipeline-223-hg38-pe-v2 ran the full pipeline with Galaxy-staged extension-less input paths; adapter autodetection silently failed, and the untrimmed alignment (5,000,000 reads) gave N_opt 13636, reported directly.</t>
+          <t>UDT encode-atac-pipeline-v2-2-3-run-v4 ran on extension-less Galaxy-staged FASTQ paths, so adapters were not trimmed; the agent also switched to the older v1 hg38_caper.tsv blacklist, a minor contribution; N_opt 13653.</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>galaxy_codex_deepseek_v4_pro_0813_r2</t>
+          <t>galaxy_codex_gpt_5_6_luna_r1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (Codex)</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>answer_producing</t>
+          <t>failed_only</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>udt</t>
+          <t>local_shell</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>133; 269; 304; 306</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>247; 264; 274; 286</t>
+          <t>99; 110; 115; 126; 133; 142; 185; 239; 269</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>UDT encode-atac-run-v4 ran the pipeline with Galaxy-bound dataset_*.dat FASTQ paths passed straight into the input JSON; extension-based adapter detection found nothing, so reads were untrimmed and N_opt was 13636.</t>
+          <t>All UDT jobs (MCP, direct-API and workflow routes) failed before command rendering. The agent then copied 13636 from answer.txt/qc.json in an earlier pilot history; the copied answer, not its own computation, set the result.</t>
         </is>
       </c>
     </row>
@@ -4555,12 +4555,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>galaxy_codex_deepseek_v4_pro_0813_r3</t>
+          <t>galaxy_codex_gpt_5_6_luna_r2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (Codex)</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4585,17 +4585,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>137; 294</t>
+          <t>453</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>204; 216; 220; 230; 294</t>
+          <t>411; 420; 432; 453</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>UDT encode-atac-pipeline-v2-2-3-run-v4 ran on extension-less Galaxy-staged FASTQ paths, so adapters were not trimmed; the agent also switched to the older v1 hg38_caper.tsv blacklist, a minor contribution; N_opt 13653.</t>
+          <t>Final UDT encode-atac-pipeline-v2-2-3-q1-final-patched-local-v38 completed, but its input JSON used Galaxy-staged dataset_*.dat FASTQ paths; extension-based adapter detection silently disabled trimming, giving N_opt 13636.</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r1</t>
+          <t>galaxy_codex_gpt_5_6_luna_r3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4627,32 +4627,32 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>local_shell</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>133; 269; 304; 306</t>
+          <t>458</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>99; 110; 115; 126; 133; 142; 185; 239; 269</t>
+          <t>423; 432; 443; 458</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>All UDT jobs (MCP, direct-API and workflow routes) failed before command rendering. The agent then copied 13636 from answer.txt/qc.json in an earlier pilot history; the copied answer, not its own computation, set the result.</t>
+          <t>UDT encode-atac-pipeline-full-v10 completed the full pipeline on extension-less Galaxy-staged FASTQ paths; adapter autodetection silently failed (untrimmed, 5,000,000 reads), giving N_opt 13636.</t>
         </is>
       </c>
     </row>
@@ -4664,22 +4664,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>encode-atac-pipeline-q1</t>
+          <t>ep-interactions-q1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r2</t>
+          <t>galaxy_codex_gpt_5_5_r1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UDT_EXECUTION</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4694,22 +4694,22 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>30; 42</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>411; 420; 432; 453</t>
+          <t>30; 36; 42</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Final UDT encode-atac-pipeline-v2-2-3-q1-final-patched-local-v38 completed, but its input JSON used Galaxy-staged dataset_*.dat FASTQ paths; extension-based adapter detection silently disabled trimming, giving N_opt 13636.</t>
+          <t>UDTs ranked pairs by contact z plus mean expression drop (signed and absolute), never testing guide concordance; EP3's single-guide effect went unpenalized and the sensitivity UDT selected EP6 (F).</t>
         </is>
       </c>
     </row>
@@ -4721,32 +4721,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>encode-atac-pipeline-q1</t>
+          <t>ep-interactions-q1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r3</t>
+          <t>galaxy_codex_gpt_5_5_r2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>UDT_EXECUTION</t>
+          <t>UDT_FAILED_NOT_DECISIVE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>answer_producing</t>
+          <t>failed_only</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>udt</t>
+          <t>galaxy_wrapper</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4756,17 +4756,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>67; 72; 118</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>423; 432; 443; 458</t>
+          <t>87; 102; 110</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>UDT encode-atac-pipeline-full-v10 completed the full pipeline on extension-less Galaxy-staged FASTQ paths; adapter autodetection silently failed (untrimmed, 5,000,000 reads), giving N_opt 13636.</t>
+          <t>Integration UDT failed at rendering. Its stated design (L82: contact residuals plus fold-change summary) matched the fallback; guide-averaged Datamash summaries computed before the UDT hid EP3's single-guide effect and gave F. Script not preserved.</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r1</t>
+          <t>galaxy_codex_gpt_5_5_r3</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4793,37 +4793,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>UDT_CODE</t>
+          <t>UDT_FAILED_NOT_DECISIVE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>answer_producing</t>
+          <t>failed_only</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>udt</t>
+          <t>galaxy_wrapper</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>30; 42</t>
+          <t>30; 98; 107; 114</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>30; 36; 42</t>
+          <t>35; 52; 55</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>UDTs ranked pairs by contact z plus mean expression drop (signed and absolute), never testing guide concordance; EP3's single-guide effect went unpenalized and the sensitivity UDT selected EP6 (F).</t>
+          <t>UDT rule stated at L30 penalized pairs lacking contact enrichment and expression decrease, with no guide-concordance test; after three rendering failures, Datamash grouped by pair and condition applied the same logic, giving F.</t>
         </is>
       </c>
     </row>
@@ -4835,12 +4835,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ep-interactions-q1</t>
+          <t>exogenous-mix-reads-q1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r2</t>
+          <t>galaxy_codex_gpt_5_5_r1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4850,37 +4850,37 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>UDT_FAILED_NOT_DECISIVE</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>galaxy_wrapper</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>67; 72; 118</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>87; 102; 110</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Integration UDT failed at rendering. Its stated design (L82: contact residuals plus fold-change summary) matched the fallback; guide-averaged Datamash summaries computed before the UDT hid EP3's single-guide effect and gave F. Script not preserved.</t>
+          <t>Single UDT fitted and scored k-mer estimators on the same reference reads (in-sample, separation 1.0) and returned their median 0.496, rounded to 50; held-out estimates give 30.</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ep-interactions-q1</t>
+          <t>exogenous-mix-reads-q1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>UDT_FAILED_NOT_DECISIVE</t>
+          <t>UDT_EXECUTION</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4927,17 +4927,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>30; 98; 107; 114</t>
+          <t>30; 55; 62; 171; 172; 177</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>35; 52; 55</t>
+          <t>30; 55; 58; 61; 170</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>UDT rule stated at L30 penalized pairs lacking contact enrichment and expression decrease, with no guide-concordance test; after three rendering failures, Datamash grouped by pair and condition applied the same logic, giving F.</t>
+          <t>All UDTs, including printf/cat probes, failed before rendering; run fell back to exact-sequence join1 counts with a coverage correction done in reasoning, yielding 40. Task entry attributes the miss partly to this forced route.</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r1</t>
+          <t>galaxy_codex_deepseek_v4_pro_0813_r3</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4984,17 +4984,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>156; 164; 168</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>130; 168</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Single UDT fitted and scored k-mer estimators on the same reference reads (in-sample, separation 1.0) and returned their median 0.496, rounded to 50; held-out estimates give 30.</t>
+          <t>Final UDT exo-fraction-v1 (L168) estimated the fraction as mix density of exo-exclusive k-mers over the in-sample exo-reference density, mean 0.516 for k=20-40, rounded to 50; no held-out fitting. Method prototyped locally first (L156, L164).</t>
         </is>
       </c>
     </row>
@@ -5006,12 +5006,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>exogenous-mix-reads-q1</t>
+          <t>exogenous-mix-reads-q2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r3</t>
+          <t>galaxy_codex_gpt_5_5_r1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5021,37 +5021,37 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>UDT_EXECUTION</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>galaxy_wrapper</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>30; 55; 62; 171; 172; 177</t>
+          <t>39; 41</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>30; 55; 58; 61; 170</t>
+          <t>26; 32; 35; 38; 41</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>All UDTs, including printf/cat probes, failed before rendering; run fell back to exact-sequence join1 counts with a coverage correction done in reasoning, yielding 40. Task entry attributes the miss partly to this forced route.</t>
+          <t>UDT klf4-final-exogenous-percent-v1 encoded record-prefix provenance (592/691 exo records in mix) as exogenous fraction, returning 90; nested-prefix files carry no exogenous signal, so reference is NA.</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r1</t>
+          <t>galaxy_codex_gpt_5_5_r2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5078,37 +5078,37 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UDT_CODE</t>
+          <t>UDT_FAILED_NOT_DECISIVE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>answer_producing</t>
+          <t>failed_only</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>udt</t>
+          <t>galaxy_wrapper</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>39; 41</t>
+          <t>136; 168; 170; 173</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>26; 32; 35; 38; 41</t>
+          <t>22; 63; 70; 75; 78; 81</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>UDT klf4-final-exogenous-percent-v1 encoded record-prefix provenance (592/691 exo records in mix) as exogenous fraction, returning 90; nested-prefix files carry no exogenous signal, so reference is NA.</t>
+          <t>Final-estimate UDT failed pre-render (L22); seqkit marker-count fallback answered 90 via the same record-identity reasoning that working UDTs in r1 and Sol r1 used to reach 90. Failure did not decide the answer.</t>
         </is>
       </c>
     </row>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r2</t>
+          <t>galaxy_codex_gpt_5_5_r3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5155,17 +5155,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>136; 168; 170; 173</t>
+          <t>219; 224; 227</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>22; 63; 70; 75; 78; 81</t>
+          <t>25; 62; 65; 68; 77; 80; 88; 91</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Final-estimate UDT failed pre-render (L22); seqkit marker-count fallback answered 90 via the same record-identity reasoning that working UDTs in r1 and Sol r1 used to reach 90. Failure did not decide the answer.</t>
+          <t>Diagnostic UDT (answer route) failed pre-render (L25); join1/datamash fallback found 592/691 mix reads in exo and answered 90, the same record-identity error the working UDTs in r1 and Sol r1 made.</t>
         </is>
       </c>
     </row>
@@ -5182,47 +5182,47 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r3</t>
+          <t>galaxy_codex_gpt_5_6_sol_r1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>UDT_FAILED_NOT_DECISIVE</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>galaxy_wrapper</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>219; 224; 227</t>
+          <t>24; 28</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>25; 62; 65; 68; 77; 80; 88; 91</t>
+          <t>23; 28</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Diagnostic UDT (answer route) failed pre-render (L25); join1/datamash fallback found 592/691 mix reads in exo and answered 90, the same record-identity error the working UDTs in r1 and Sol r1 made.</t>
+          <t>UDT klf4-exogenous-fraction-estimator-v1 applied a marker-rate correction (0.871) and record-identity fraction (0.857), rounding to 90; nested-prefix files provide no exogenous-specific signal, reference NA.</t>
         </is>
       </c>
     </row>
@@ -5234,52 +5234,52 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>exogenous-mix-reads-q2</t>
+          <t>finding-geo-q1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_sol_r1</t>
+          <t>galaxy_codex_gpt_5_5_r1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UDT_CODE</t>
+          <t>AFTER_UDT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>answer_producing</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>udt</t>
+          <t>web_or_knowledge</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>24; 28</t>
+          <t>399; 420; 425</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>23; 28</t>
+          <t>97; 158; 417</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>UDT klf4-exogenous-fraction-estimator-v1 applied a marker-rate correction (0.871) and record-identity fraction (0.857), rounding to 90; nested-prefix files provide no exogenous-specific signal, reference NA.</t>
+          <t>summarize-gse117542 UDT correctly showed no match (85,103 cells, 2,251 barcodes overlapping); the agent overrode it after a web barcode search and answered GSE117542 as best-supported. Marker UDT outputs were misread as retina/hypothalamus.</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r1</t>
+          <t>galaxy_codex_gpt_5_5_r2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>399; 420; 425</t>
+          <t>139; 248; 261; 264</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>97; 158; 417</t>
+          <t>36; 59; 138; 217; 223; 239; 247</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>summarize-gse117542 UDT correctly showed no match (85,103 cells, 2,251 barcodes overlapping); the agent overrode it after a web barcode search and answered GSE117542 as best-supported. Marker UDT outputs were misread as retina/hypothalamus.</t>
+          <t>Marker UDTs (L59, L138) were read as hypothalamic; the RDS-inspection UDT showed GSE132730 E15 had 8,862 cells, not a match (L247-L248), yet the agent answered GSE132730 on biological similarity (L261, L264).</t>
         </is>
       </c>
     </row>
@@ -5353,27 +5353,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>galaxy_codex_deepseek_v4_pro_0813_r1</t>
+          <t>galaxy_codex_gpt_5_5_r3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (Codex)</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>UDT_CODE</t>
+          <t>AFTER_UDT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>answer_producing</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>udt</t>
+          <t>web_or_knowledge</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5383,17 +5383,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>210; 238</t>
+          <t>395; 580; 583</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>234; 238</t>
+          <t>53; 257; 272; 346; 390; 392; 394; 496</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>h5-compare UDT tested only barcode and gene membership against GSE135737's raw 737,280-barcode whitelist matrix, which trivially contains all barcodes, reporting matches=True. The same weak test first ran locally at L210.</t>
+          <t>Galaxy comparison UDTs ruled out GSE153164 (27,998 genes, 7-11k cells; L390-L395). After exhausting other candidates, the agent answered GSE153164 anyway without new evidence (L580, L583); no exact matrix match was ever found.</t>
         </is>
       </c>
     </row>
@@ -6341,17 +6341,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>UDT_FAILED_NOT_DECISIVE</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>local_shell</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>128; 280</t>
+          <t>171</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>143; 161; 164; 192; 196</t>
+          <t>147; 171; 187</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>UDT route (rule diagnostic, then planned final count) failed pre-render. Local Python fallback applied the GSM-only rule fixed at L128 before any UDT, missing ENCSR-to-Cistrome ENCODE matches: 2,411. Failure not decisive.</t>
+          <t>UDT cistrome-old-api-overlap-validation-v1 (L171) matched Borzoi GSM/ENCSR keywords to Sei Cistrome IDs, 1,263 tracks (1300), omitting the ENCODE-dbxref GSM route; failed UDT L187 was a one-accession side check.</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>protein-shape-q1</t>
+          <t>perturb-seq-align-q1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r1</t>
+          <t>galaxy_codex_gpt_5_5_r3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>REFERENCE_OR_EVALUATOR</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -7610,18 +7610,22 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>moderate</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>88; 96; 97</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>61; 69; 87; 96</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>UDT protein-letter-projection-v1 ranked T first (all-atom F1 0.579). Task entry judges T a defensible side-view reading of an underspecified prompt, though key F (Howarth 3J04) is well founded.</t>
+          <t>No task entry exists. Final UDT mapped reference non-NT guide category order onto anonymized query guide numbers (L88, L96), an unfounded assumption, giving guide16,guide15,guide14 (L97); expression-alignment UDT configurations had pointed to guide18/guide13 (L69).</t>
         </is>
       </c>
     </row>
@@ -7633,17 +7637,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>protein-shape-q1</t>
+          <t>phase-chain-q1</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r2</t>
+          <t>galaxy_codex_deepseek_v4_pro_0813_r2</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7663,22 +7667,22 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>216; 240</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>22; 25; 31</t>
+          <t>240</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>UDT pdb-shape-letter-score-v1 scored block-letter templates with 'stretch' normalization on C-alpha traces and ranked N first; the agent reported N directly. The scoring method, not execution, produced a letter the entry does not call defensible.</t>
+          <t>UDT readback_phase_v1 (L240) output was submitted verbatim. Its script set deletion-site symbols to ['I','D'] (L216), writing the non-deleted allele as I instead of its base (G/A/G at sites 4, 6, 7); SNPs and phase match reference.</t>
         </is>
       </c>
     </row>
@@ -7695,7 +7699,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r3</t>
+          <t>galaxy_codex_gpt_5_5_r1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -7710,12 +7714,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>local_shell</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7726,12 +7730,12 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>25; 45; 54; 57; 60; 94</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>All six UDTs failed before command rendering; T came from a local run of the projection script. Task entry deems T a defensible reading of an underspecified prompt, so no execution error is located.</t>
+          <t>UDT protein-letter-projection-v1 ranked T first (all-atom F1 0.579). Task entry judges T a defensible side-view reading of an underspecified prompt, though key F (Howarth 3J04) is well founded.</t>
         </is>
       </c>
     </row>
@@ -7748,17 +7752,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_sol_r1</t>
+          <t>galaxy_codex_gpt_5_5_r2</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>REFERENCE_OR_EVALUATOR</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -7776,15 +7780,19 @@
           <t>moderate</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>16; 23; 33; 40</t>
+          <t>22; 25; 31</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>UDT projection scans and montage showed a crossbar with central stem; agent chose T over the silhouette UDT's narrow R ranking. Task entry judges T a defensible visual reading of an underspecified task.</t>
+          <t>UDT pdb-shape-letter-score-v1 scored block-letter templates with 'stretch' normalization on C-alpha traces and ranked N first; the agent reported N directly. The scoring method, not execution, produced a letter the entry does not call defensible.</t>
         </is>
       </c>
     </row>
@@ -7801,12 +7809,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_sol_r2</t>
+          <t>galaxy_codex_gpt_5_5_r3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7821,7 +7829,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>galaxy_wrapper</t>
+          <t>local_shell</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7832,12 +7840,12 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t>16; 21; 30; 38; 75</t>
+          <t>25; 45; 54; 57; 60; 94</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>All UDTs failed before command rendering; T came from Galaxy wrapper scatterplots of extracted coordinates judged by eye. Task entry deems T a defensible reading of the underspecified prompt.</t>
+          <t>All six UDTs failed before command rendering; T came from a local run of the projection script. Task entry deems T a defensible reading of an underspecified prompt, so no execution error is located.</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7862,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_sol_r3</t>
+          <t>galaxy_codex_gpt_5_6_sol_r1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7869,12 +7877,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>galaxy_wrapper</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7885,12 +7893,12 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t>16; 25; 49; 51; 60</t>
+          <t>16; 23; 33; 40</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>All five UDTs failed before command rendering; T came from Galaxy wrapper scatterplots (x/y view 'top bar plus central stem'). Task entry cites this run and deems T a defensible visual reading.</t>
+          <t>UDT projection scans and montage showed a crossbar with central stem; agent chose T over the silhouette UDT's narrow R ranking. Task entry judges T a defensible visual reading of an underspecified task.</t>
         </is>
       </c>
     </row>
@@ -7907,17 +7915,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r1</t>
+          <t>galaxy_codex_gpt_5_6_sol_r2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>UDT_FAILED_NOT_DECISIVE</t>
+          <t>REFERENCE_OR_EVALUATOR</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7935,19 +7943,15 @@
           <t>moderate</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>805; 878</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>29; 38; 54; 58; 73; 85; 197</t>
+          <t>16; 21; 30; 38; 75</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>The failed UDT (shape_diag.py) only rendered PCA C-alpha projections for visual reading, with no letter scoring. The wrapper fallback rendered the same kinds of projections, and the agent's visual judgement of them gave Z.</t>
+          <t>All UDTs failed before command rendering; T came from Galaxy wrapper scatterplots of extracted coordinates judged by eye. Task entry deems T a defensible reading of the underspecified prompt.</t>
         </is>
       </c>
     </row>
@@ -7964,12 +7968,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r2</t>
+          <t>galaxy_codex_gpt_5_6_sol_r3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7995,12 +7999,12 @@
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
-          <t>41; 71; 80; 90; 141; 143; 217</t>
+          <t>16; 25; 49; 51; 60</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>All UDTs failed before command rendering; T came from Galaxy wrapper scatterplots of C-alpha coordinates judged visually. Task entry deems T a defensible reading of the underspecified prompt.</t>
+          <t>All five UDTs failed before command rendering; T came from Galaxy wrapper scatterplots (x/y view 'top bar plus central stem'). Task entry cites this run and deems T a defensible visual reading.</t>
         </is>
       </c>
     </row>
@@ -8012,32 +8016,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>reverse-search-gwas-q1</t>
+          <t>protein-shape-q1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r1</t>
+          <t>galaxy_codex_gpt_5_6_luna_r1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AFTER_UDT</t>
+          <t>UDT_FAILED_NOT_DECISIVE</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>failed_only</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>web_or_knowledge</t>
+          <t>galaxy_wrapper</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8047,17 +8051,17 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>279; 295; 298</t>
+          <t>805; 878</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>25; 81; 140; 152; 165; 171; 185; 196; 202; 210; 221; 255; 294</t>
+          <t>29; 38; 54; 58; 73; 85; 197</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>UDTs correctly extracted lead loci and found no exact P-value match for any candidate, including 29403010 (L294). The agent still chose it from web locus-pattern and trait/sample-size similarity (L279, L295).</t>
+          <t>The failed UDT (shape_diag.py) only rendered PCA C-alpha projections for visual reading, with no letter scoring. The wrapper fallback rendered the same kinds of projections, and the agent's visual judgement of them gave Z.</t>
         </is>
       </c>
     </row>
@@ -8069,52 +8073,52 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>reverse-search-gwas-q1</t>
+          <t>protein-shape-q1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r2</t>
+          <t>galaxy_codex_gpt_5_6_luna_r2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AFTER_UDT</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>local_shell</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>398; 399</t>
+          <t>37; 61</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>32; 45; 215; 227; 247; 261</t>
+          <t>37; 43; 55; 61</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>UDT lead-region scan (L45) was correct and confirmation UDTs rejected GCST90241623. The final PMID came from local locus-overlap scoring of GWAS Catalog associations over those leads (L398), not an exact P-value match.</t>
+          <t>UDT pdb-letter-score (v1-v4, L37-L61) rasterised C-alpha projections over 10,368 views and scored glyph overlap; N ranked first (0.409) over T and H, F tenth (0.298). Answer N taken directly; task entry supports F (PDB 3J04).</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8130,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>reverse-search-gwas-q1</t>
+          <t>reverse-encode-q1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r3</t>
+          <t>galaxy_codex_gpt_5_5_r2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -8146,32 +8150,32 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>web_or_knowledge</t>
+          <t>local_shell</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>213; 215; 216</t>
+          <t>55; 75; 146; 159; 171</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>46; 65</t>
+          <t>52; 55; 75; 115; 127; 152; 158; 164; 167; 170</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>The failed top-hit UDT was meant to rank lead variants; a Galaxy Sort wrapper produced the same lead rows. The wrong PMID came later from web/GWAS Catalog lookup of an FCGR3B protein accession (L213-L215).</t>
+          <t>No task entry exists. Galaxy bigWig screen UDTs could not open remote files (L55, L75); local fallback ran the same correlation screen (L146). Full-track UDTs showed ENCSR396ZIN non-exact (L158-L159), but agent answered it; shortlisted ENCSR597URK untested (L98).</t>
         </is>
       </c>
     </row>
@@ -8188,27 +8192,27 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_sol_r1</t>
+          <t>galaxy_codex_gpt_5_5_r1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>UDT_CODE</t>
+          <t>AFTER_UDT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>answer_producing</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>udt</t>
+          <t>web_or_knowledge</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8218,17 +8222,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>84; 103</t>
+          <t>279; 295; 298</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>44; 59; 103</t>
+          <t>25; 81; 140; 152; 165; 171; 185; 196; 202; 210; 221; 255; 294</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>After a web locus-pattern search chose BioBank Japan (L84), the final UDT scored only that PMID's catalog leads by 1-Mb locus overlap (L103), not exact P values, and so confirmed the wrong PMID 29403010.</t>
+          <t>UDTs correctly extracted lead loci and found no exact P-value match for any candidate, including 29403010 (L294). The agent still chose it from web locus-pattern and trait/sample-size similarity (L279, L295).</t>
         </is>
       </c>
     </row>
@@ -8245,27 +8249,27 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_sol_r3</t>
+          <t>galaxy_codex_gpt_5_5_r2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>UDT_CODE</t>
+          <t>AFTER_UDT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>answer_producing</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>udt</t>
+          <t>local_shell</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8275,17 +8279,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>59; 67; 76</t>
+          <t>398; 399</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>37; 67; 76</t>
+          <t>32; 45; 215; 227; 247; 261</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Right study found, but the matching UDT compared lead variant IDs only with the v1 pips.tsv (no P values). It inferred cohort eur94082, and the finalize UDT emitted preprint PMID 38798542, not the revision record.</t>
+          <t>UDT lead-region scan (L45) was correct and confirmation UDTs rejected GCST90241623. The final PMID came from local locus-overlap scoring of GWAS Catalog associations over those leads (L398), not an exact P-value match.</t>
         </is>
       </c>
     </row>
@@ -8302,17 +8306,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>galaxy_codex_deepseek_v4_pro_0813_r1</t>
+          <t>galaxy_codex_gpt_5_5_r3</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (Codex)</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>NOT_ON_PATH</t>
+          <t>UDT_FAILED_NOT_DECISIVE</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -8327,22 +8331,22 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>759; 1104; 1194</t>
+          <t>213; 215; 216</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>212; 228; 230; 238; 244</t>
+          <t>46; 65</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>The UDTs were a 'Probe GWAS API' job after Galaxy URL fetches failed, then minimal render smoke tests; all failed pre-rendering. The answer came later from GWAS Catalog lookups of rs72717048 (web, Galaxy grep). Probe script not visible.</t>
+          <t>The failed top-hit UDT was meant to rank lead variants; a Galaxy Sort wrapper produced the same lead rows. The wrong PMID came later from web/GWAS Catalog lookup of an FCGR3B protein accession (L213-L215).</t>
         </is>
       </c>
     </row>
@@ -8359,27 +8363,27 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r3</t>
+          <t>galaxy_codex_gpt_5_6_sol_r1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>UDT_FAILED_NOT_DECISIVE</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>web_or_knowledge</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8389,17 +8393,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>6068; 6191; 6297</t>
+          <t>84; 103</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>2280; 2292; 2294; 2325; 6210; 6253</t>
+          <t>44; 59; 103</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>The IgG-glycan candidate was fixed by locus-pattern search before the UDT (L6068, L6191). The exact-match verification UDT failed and the agent submitted that candidate; a working check would likely reject it, not yield 41491094.</t>
+          <t>After a web locus-pattern search chose BioBank Japan (L84), the final UDT scored only that PMID's catalog leads by 1-Mb locus overlap (L103), not exact P values, and so confirmed the wrong PMID 29403010.</t>
         </is>
       </c>
     </row>
@@ -8411,7 +8415,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>sample-swap-atac-q1</t>
+          <t>reverse-search-gwas-q1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8441,22 +8445,22 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>67; 100; 107</t>
+          <t>59; 67; 76</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>67; 100; 107</t>
+          <t>37; 67; 76</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Evidence UDT scored swaps only by weak promoter-marker signatures and library size versus GEO file size, which cannot detect the same-size Cloaca/Stomach swap; finalize UDT wrote None.</t>
+          <t>Right study found, but the matching UDT compared lead variant IDs only with the v1 pips.tsv (no P values). It inferred cohort eur94082, and the finalize UDT emitted preprint PMID 38798542, not the revision record.</t>
         </is>
       </c>
     </row>
@@ -8468,22 +8472,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>spatial-sim-q2</t>
+          <t>reverse-search-gwas-q1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_sol_r2</t>
+          <t>galaxy_codex_deepseek_v4_pro_0813_r1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>UDT_EXECUTION</t>
+          <t>NOT_ON_PATH</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -8493,27 +8497,27 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>galaxy_wrapper</t>
+          <t>web_or_knowledge</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>31; 48; 539; 541; 553</t>
+          <t>759; 1104; 1194</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>21; 28; 33; 47</t>
+          <t>212; 228; 230; 238; 244</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>UDT execution was unavailable (image not schedulable; even a wc probe failed) before the planned custom proximity UDT was written. Forced squidpy nhood_enrichment wrapper tested adjacency of dominant labels, missing Fibroblast_Stroma's distance-scale proximity.</t>
+          <t>The UDTs were a 'Probe GWAS API' job after Galaxy URL fetches failed, then minimal render smoke tests; all failed pre-rendering. The answer came later from GWAS Catalog lookups of rs72717048 (web, Galaxy grep). Probe script not visible.</t>
         </is>
       </c>
     </row>
@@ -8525,32 +8529,32 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>three-way-barnyard-q2</t>
+          <t>reverse-search-gwas-q1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>galaxy_codex_deepseek_v4_pro_0813_r1</t>
+          <t>galaxy_codex_gpt_5_6_luna_r3</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (Codex)</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>UDT_CODE</t>
+          <t>UDT_FAILED_NOT_DECISIVE</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>answer_producing</t>
+          <t>failed_only</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>udt</t>
+          <t>web_or_knowledge</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8560,17 +8564,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>112; 120</t>
+          <t>6068; 6191; 6297</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>104; 112; 116; 120</t>
+          <t>2280; 2292; 2294; 2325; 6210; 6253</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Final UDT assigned all 600 barcodes by plurality (human 144), giving 20;30;50, although its own classify UDT showed 50/150/300 (10;30;60) at purity &gt;=0.8. Borderline given the entry's underspecification note.</t>
+          <t>The IgG-glycan candidate was fixed by locus-pattern search before the UDT (L6068, L6191). The exact-match verification UDT failed and the agent submitted that candidate; a working check would likely reject it, not yield 41491094.</t>
         </is>
       </c>
     </row>
@@ -8582,52 +8586,52 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>three-way-barnyard-q2</t>
+          <t>sample-swap-atac-q1</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>galaxy_codex_deepseek_v4_pro_0813_r3</t>
+          <t>galaxy_codex_gpt_5_6_sol_r3</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (Codex)</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>UDT_FAILED_NOT_DECISIVE</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>galaxy_wrapper</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1112; 1120; 1152; 1248; 1250</t>
+          <t>67; 100; 107</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>336; 358; 366; 372; 374; 376; 398; 404; 474</t>
+          <t>67; 100; 107</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>All UDTs failed pre-render; the failed classifier script used the same case-sensitive marker-symbol lookup as the scanpy score_genes fallback, so it would also have missed mouse markers. Failure likely not decisive.</t>
+          <t>Evidence UDT scored swaps only by weak promoter-marker signatures and library size versus GEO file size, which cannot detect the same-size Cloaca/Stomach swap; finalize UDT wrote None.</t>
         </is>
       </c>
     </row>
@@ -8639,32 +8643,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>three-way-barnyard-q2</t>
+          <t>sample-swap-rna-q1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r1</t>
+          <t>galaxy_codex_gpt_5_5_r3</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>UDT_EXECUTION</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>failed_only</t>
+          <t>answer_producing</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>galaxy_wrapper</t>
+          <t>udt</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8674,17 +8678,17 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>558; 577; 787; 794</t>
+          <t>61; 111; 112</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>154; 165; 167; 171; 218; 220</t>
+          <t>61; 96; 99; 111</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Planned read-level UDT classifier failed server-wide pre-render; forced Alevin route needed a UMI-tools knee whitelist (235 of 600 barcodes), dropping mostly pig cells and giving 51/76/108 = 20;30;50.</t>
+          <t>Circular marker check: UDT extracted each column's own top-specific genes (diagnostic UDT L61); every marker peaked in its labelled column (L111), so None was answered (L112) despite reciprocal epidermis-tailbud_neural neighbours (L62). Annotation UDT OOMs were side lookups.</t>
         </is>
       </c>
     </row>
@@ -8696,17 +8700,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>three-way-barnyard-q2</t>
+          <t>spatial-sim-q2</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_luna_r2</t>
+          <t>galaxy_codex_gpt_5_6_sol_r2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8731,17 +8735,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>442; 471; 765</t>
+          <t>31; 48; 539; 541; 553</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>36; 61</t>
+          <t>21; 28; 33; 47</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Barnyard UDT classifier failed pre-render; fallback Alevin required a UMI-tools whitelist of 237 barcodes, re-filtering pre-thresholded cells to 52/74/112 = 20;30;50. The error comes from the forced wrapper route.</t>
+          <t>UDT execution was unavailable (image not schedulable; even a wc probe failed) before the planned custom proximity UDT was written. Forced squidpy nhood_enrichment wrapper tested adjacency of dominant labels, missing Fibroblast_Stroma's distance-scale proximity.</t>
         </is>
       </c>
     </row>
@@ -8753,12 +8757,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>tissue-fibroblast-q1</t>
+          <t>three-way-barnyard-q2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r1</t>
+          <t>galaxy_codex_gpt_5_5_r3</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8768,7 +8772,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>REFERENCE_OR_EVALUATOR</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -8786,15 +8790,19 @@
           <t>moderate</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>72; 80; 81</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>24; 33; 72; 106; 111; 117; 123</t>
+          <t>61; 69; 72; 80</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>The exact count-vector match UDT returned the atlas Tissue labels Omentum,Bone. The task entry calls this an honest source-metadata lookup on an ambiguous item; the key follows expression (Lung). No execution error.</t>
+          <t>Species-calling UDT (combined Ensembl cDNA, minimap2, MAPQ&gt;=10; 694,796 of 962,246 aligned reads discarded) called 242 mouse (entry: ~150 pure) and 35 human singlets (L72); threshold-scan UDT kept 10;40;50 across cutoffs (L80); submitted L81.</t>
         </is>
       </c>
     </row>
@@ -8806,22 +8814,22 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>tissue-fibroblast-q1</t>
+          <t>three-way-barnyard-q2</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_5_r2</t>
+          <t>galaxy_codex_deepseek_v4_pro_0813_r1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>REFERENCE_OR_EVALUATOR</t>
+          <t>UDT_CODE</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -8839,15 +8847,19 @@
           <t>moderate</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>112; 120</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>27; 33; 81; 87; 93; 99; 105; 111</t>
+          <t>104; 112; 116; 120</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>The exact-column match UDT (L111) superseded an earlier row-index lookup and returned the atlas labels Omentum,Bone. The task entry treats this as a defensible source-label reading of an ambiguous item. No execution error.</t>
+          <t>Final UDT assigned all 600 barcodes by plurality (human 144), giving 20;30;50, although its own classify UDT showed 50/150/300 (10;30;60) at purity &gt;=0.8. Borderline given the entry's underspecification note.</t>
         </is>
       </c>
     </row>
@@ -8859,48 +8871,52 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>tissue-fibroblast-q1</t>
+          <t>three-way-barnyard-q2</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_sol_r2</t>
+          <t>galaxy_codex_deepseek_v4_pro_0813_r3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>REFERENCE_OR_EVALUATOR</t>
+          <t>UDT_FAILED_NOT_DECISIVE</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>answer_producing</t>
+          <t>failed_only</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>udt</t>
+          <t>galaxy_wrapper</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>moderate</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1112; 1120; 1152; 1248; 1250</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>20; 25; 63; 78; 83</t>
+          <t>336; 358; 366; 372; 374; 376; 398; 404; 474</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>The exact full-count match UDT found unique source cells and returned the atlas Tissue labels Omentum,Bone. The task entry deems the metadata answer defensible on an ambiguous item; the key follows expression.</t>
+          <t>All UDTs failed pre-render; the failed classifier script used the same case-sensitive marker-symbol lookup as the scanpy score_genes fallback, so it would also have missed mouse markers. Failure likely not decisive.</t>
         </is>
       </c>
     </row>
@@ -8912,32 +8928,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>tissue-fibroblast-q1</t>
+          <t>three-way-barnyard-q2</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>galaxy_codex_gpt_5_6_sol_r3</t>
+          <t>galaxy_codex_gpt_5_6_luna_r1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>GPT-5.6 Sol</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>REFERENCE_OR_EVALUATOR</t>
+          <t>UDT_EXECUTION</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>answer_producing</t>
+          <t>failed_only</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>udt</t>
+          <t>galaxy_wrapper</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8945,15 +8961,19 @@
           <t>moderate</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>558; 577; 787; 794</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>19; 25; 109; 120; 132; 139</t>
+          <t>154; 165; 167; 171; 218; 220</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>The exact sparse fingerprint match UDT (L139) returned the atlas labels Omentum,Bone. Per the task entry this is an honest source-metadata lookup on an ambiguous item; the key follows the cell's expression.</t>
+          <t>Planned read-level UDT classifier failed server-wide pre-render; forced Alevin route needed a UMI-tools knee whitelist (235 of 600 barcodes), dropping mostly pig cells and giving 51/76/108 = 20;30;50.</t>
         </is>
       </c>
     </row>
@@ -8965,32 +8985,32 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>tissue-fibroblast-q1</t>
+          <t>three-way-barnyard-q2</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>galaxy_codex_deepseek_v4_pro_0813_r1</t>
+          <t>galaxy_codex_gpt_5_6_luna_r2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (Codex)</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>REFERENCE_OR_EVALUATOR</t>
+          <t>UDT_EXECUTION</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>answer_producing</t>
+          <t>failed_only</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>udt</t>
+          <t>galaxy_wrapper</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8998,15 +9018,19 @@
           <t>moderate</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>442; 471; 765</t>
+        </is>
+      </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>78; 156; 158; 218; 222; 226</t>
+          <t>36; 61</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>The exact-count match UDT (L226) found unique source cells labeled Omentum and Bone. The task entry treats this atlas-label answer as defensible on an ambiguous item. No execution error to locate.</t>
+          <t>Barnyard UDT classifier failed pre-render; fallback Alevin required a UMI-tools whitelist of 237 barcodes, re-filtering pre-thresholded cells to 52/74/112 = 20;30;50. The error comes from the forced wrapper route.</t>
         </is>
       </c>
     </row>
@@ -9023,12 +9047,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>galaxy_codex_deepseek_v4_pro_0813_r2</t>
+          <t>galaxy_codex_gpt_5_5_r1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro (Codex)</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -9054,12 +9078,12 @@
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
-          <t>56; 64; 82; 144; 146; 150; 156; 214; 224; 232; 238; 244</t>
+          <t>24; 33; 72; 106; 111; 117; 123</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>The exact-match UDT (L244) returned atlas Tissue labels Omentum,Bone for the matched source cells. The task entry treats this metadata answer as defensible on an ambiguous item; the key follows expression.</t>
+          <t>The exact count-vector match UDT returned the atlas Tissue labels Omentum,Bone. The task entry calls this an honest source-metadata lookup on an ambiguous item; the key follows expression (Lung). No execution error.</t>
         </is>
       </c>
     </row>
@@ -9076,47 +9100,255 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>galaxy_codex_deepseek_v4_pro_0813_r3</t>
+          <t>galaxy_codex_gpt_5_5_r2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t>GPT-5.5</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>REFERENCE_OR_EVALUATOR</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>answer_producing</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>udt</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>27; 33; 81; 87; 93; 99; 105; 111</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>The exact-column match UDT (L111) superseded an earlier row-index lookup and returned the atlas labels Omentum,Bone. The task entry treats this as a defensible source-label reading of an ambiguous item. No execution error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>tissue-fibroblast-q1</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>galaxy_codex_gpt_5_6_sol_r2</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Sol</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>REFERENCE_OR_EVALUATOR</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>answer_producing</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>udt</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>20; 25; 63; 78; 83</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>The exact full-count match UDT found unique source cells and returned the atlas Tissue labels Omentum,Bone. The task entry deems the metadata answer defensible on an ambiguous item; the key follows expression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>tissue-fibroblast-q1</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>galaxy_codex_gpt_5_6_sol_r3</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Sol</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>REFERENCE_OR_EVALUATOR</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>answer_producing</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>udt</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>19; 25; 109; 120; 132; 139</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>The exact sparse fingerprint match UDT (L139) returned the atlas labels Omentum,Bone. Per the task entry this is an honest source-metadata lookup on an ambiguous item; the key follows the cell's expression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>tissue-fibroblast-q1</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>galaxy_codex_deepseek_v4_pro_0813_r1</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
           <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>UDT_FAILED_NOT_DECISIVE</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>failed_only</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>galaxy_wrapper</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>REFERENCE_OR_EVALUATOR</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>answer_producing</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>udt</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>1808; 1822; 1832; 1834</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>124; 128; 136; 146; 148; 150; 170; 970; 1273; 1283</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>The failed UDTs only inspected RDS objects and exported metadata. The text-tool fallback read the same atlas Tissue labels, then treated barcode numbers as row indices, the same result GPT-5.5 r2 got from real metadata.</t>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>78; 156; 158; 218; 222; 226</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>The exact-count match UDT (L226) found unique source cells labeled Omentum and Bone. The task entry treats this atlas-label answer as defensible on an ambiguous item. No execution error to locate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>tissue-fibroblast-q1</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>galaxy_codex_deepseek_v4_pro_0813_r2</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>REFERENCE_OR_EVALUATOR</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>answer_producing</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>udt</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>56; 64; 82; 144; 146; 150; 156; 214; 224; 232; 238; 244</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>The exact-match UDT (L244) returned atlas Tissue labels Omentum,Bone for the matched source cells. The task entry treats this metadata answer as defensible on an ambiguous item; the key follows expression.</t>
         </is>
       </c>
     </row>
@@ -38530,11 +38762,11 @@
         <v>1</v>
       </c>
       <c r="F754" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
@@ -38998,11 +39230,11 @@
         <v>1</v>
       </c>
       <c r="F766" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="G766" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H766" t="inlineStr">
@@ -42232,14 +42464,14 @@
         <v>1</v>
       </c>
       <c r="E849" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F849" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H849" t="inlineStr">
@@ -45511,11 +45743,11 @@
         <v>1</v>
       </c>
       <c r="F933" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G933" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H933" t="inlineStr">
@@ -45671,7 +45903,7 @@
       </c>
       <c r="G937" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H937" t="inlineStr">
@@ -49879,7 +50111,7 @@
         <v>0</v>
       </c>
       <c r="F1045" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G1045" t="inlineStr">
         <is>
@@ -49957,11 +50189,11 @@
         <v>0</v>
       </c>
       <c r="F1047" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1047" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1047" t="inlineStr">
@@ -50107,17 +50339,17 @@
         <v>3</v>
       </c>
       <c r="D1051" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1051" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1051" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1051" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>no UDT</t>
         </is>
       </c>
       <c r="H1051" t="inlineStr">
@@ -50383,7 +50615,7 @@
         <v>0</v>
       </c>
       <c r="E1058" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1058" t="n">
         <v>0</v>
@@ -50575,17 +50807,17 @@
         <v>3</v>
       </c>
       <c r="D1063" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1063" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1063" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G1063" t="inlineStr">
         <is>
-          <t>no UDT</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1063" t="inlineStr">
@@ -51043,17 +51275,17 @@
         <v>3</v>
       </c>
       <c r="D1075" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1075" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1075" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1075" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>no UDT</t>
         </is>
       </c>
       <c r="H1075" t="inlineStr">
@@ -51163,7 +51395,7 @@
         <v>0</v>
       </c>
       <c r="E1078" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1078" t="n">
         <v>0</v>
@@ -54436,17 +54668,17 @@
         <v>1</v>
       </c>
       <c r="D1162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1162" t="b">
         <v>1</v>
       </c>
       <c r="F1162" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G1162" t="inlineStr">
         <is>
-          <t>no UDT</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1162" t="inlineStr">
@@ -55183,11 +55415,11 @@
         <v>0</v>
       </c>
       <c r="F1181" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1181" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1181" t="inlineStr">
@@ -55219,14 +55451,14 @@
         <v>1</v>
       </c>
       <c r="E1182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1182" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G1182" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1182" t="inlineStr">
@@ -57793,10 +58025,10 @@
         <v>1</v>
       </c>
       <c r="E1248" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1248" t="inlineStr">
         <is>
@@ -58420,11 +58652,11 @@
         <v>1</v>
       </c>
       <c r="F1264" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G1264" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1264" t="inlineStr">
@@ -59821,14 +60053,14 @@
         <v>1</v>
       </c>
       <c r="E1300" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1300" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G1300" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1300" t="inlineStr">
@@ -59860,14 +60092,14 @@
         <v>1</v>
       </c>
       <c r="E1301" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1301" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="G1301" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1301" t="inlineStr">
@@ -60016,10 +60248,10 @@
         <v>1</v>
       </c>
       <c r="E1305" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1305" t="inlineStr">
         <is>
@@ -62203,11 +62435,11 @@
         <v>1</v>
       </c>
       <c r="F1361" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G1361" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1361" t="inlineStr">
@@ -64543,11 +64775,11 @@
         <v>1</v>
       </c>
       <c r="F1421" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1421" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1421" t="inlineStr">
@@ -65401,11 +65633,11 @@
         <v>1</v>
       </c>
       <c r="F1443" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1443" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1443" t="inlineStr">
@@ -66337,11 +66569,11 @@
         <v>1</v>
       </c>
       <c r="F1467" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G1467" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1467" t="inlineStr">
@@ -66376,11 +66608,11 @@
         <v>1</v>
       </c>
       <c r="F1468" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G1468" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1468" t="inlineStr">
@@ -66844,11 +67076,11 @@
         <v>1</v>
       </c>
       <c r="F1480" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G1480" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1480" t="inlineStr">
@@ -67312,11 +67544,11 @@
         <v>1</v>
       </c>
       <c r="F1492" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1492" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1492" t="inlineStr">
@@ -67741,11 +67973,11 @@
         <v>1</v>
       </c>
       <c r="F1503" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1503" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1503" t="inlineStr">
@@ -68170,11 +68402,11 @@
         <v>1</v>
       </c>
       <c r="F1514" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G1514" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1514" t="inlineStr">
@@ -68209,11 +68441,11 @@
         <v>1</v>
       </c>
       <c r="F1515" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1515" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1515" t="inlineStr">
@@ -68482,11 +68714,11 @@
         <v>1</v>
       </c>
       <c r="F1522" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G1522" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1522" t="inlineStr">
@@ -68638,11 +68870,11 @@
         <v>0</v>
       </c>
       <c r="F1526" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1526" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1526" t="inlineStr">
@@ -69106,11 +69338,11 @@
         <v>1</v>
       </c>
       <c r="F1538" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1538" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1538" t="inlineStr">
@@ -71879,7 +72111,7 @@
       </c>
       <c r="G1609" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1609" t="inlineStr">
@@ -71911,14 +72143,14 @@
         <v>1</v>
       </c>
       <c r="E1610" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1610" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1610" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1610" t="inlineStr">
@@ -73003,7 +73235,7 @@
         <v>1</v>
       </c>
       <c r="E1638" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1638" t="n">
         <v>1</v>
@@ -74488,11 +74720,11 @@
         <v>0</v>
       </c>
       <c r="F1676" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G1676" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1676" t="inlineStr">
@@ -75116,7 +75348,7 @@
       </c>
       <c r="G1692" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1692" t="inlineStr">
@@ -75580,11 +75812,11 @@
         <v>1</v>
       </c>
       <c r="F1704" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1704" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1704" t="inlineStr">
@@ -75730,17 +75962,17 @@
         <v>1</v>
       </c>
       <c r="D1708" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1708" t="b">
         <v>1</v>
       </c>
       <c r="F1708" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G1708" t="inlineStr">
         <is>
-          <t>no UDT</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1708" t="inlineStr">
@@ -76006,14 +76238,14 @@
         <v>1</v>
       </c>
       <c r="E1715" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1715" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G1715" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1715" t="inlineStr">
@@ -77452,11 +77684,11 @@
         <v>1</v>
       </c>
       <c r="F1752" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1752" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1752" t="inlineStr">
@@ -77647,11 +77879,11 @@
         <v>1</v>
       </c>
       <c r="F1757" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1757" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1757" t="inlineStr">
@@ -78814,14 +79046,14 @@
         <v>1</v>
       </c>
       <c r="E1787" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1787" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1787" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1787" t="inlineStr">
@@ -79753,11 +79985,11 @@
         <v>1</v>
       </c>
       <c r="F1811" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1811" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1811" t="inlineStr">
@@ -80689,11 +80921,11 @@
         <v>1</v>
       </c>
       <c r="F1835" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G1835" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1835" t="inlineStr">
@@ -80839,17 +81071,17 @@
         <v>1</v>
       </c>
       <c r="D1839" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1839" t="b">
         <v>1</v>
       </c>
       <c r="F1839" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1839" t="inlineStr">
         <is>
-          <t>no UDT</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1839" t="inlineStr">
@@ -81040,11 +81272,11 @@
         <v>1</v>
       </c>
       <c r="F1844" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1844" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1844" t="inlineStr">
@@ -82090,14 +82322,14 @@
         <v>1</v>
       </c>
       <c r="E1871" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1871" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1871" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1871" t="inlineStr">
@@ -82792,14 +83024,14 @@
         <v>1</v>
       </c>
       <c r="E1889" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1889" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G1889" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1889" t="inlineStr">
@@ -82834,11 +83066,11 @@
         <v>1</v>
       </c>
       <c r="F1890" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G1890" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1890" t="inlineStr">
@@ -83926,11 +84158,11 @@
         <v>1</v>
       </c>
       <c r="F1918" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G1918" t="inlineStr">
         <is>
-          <t>all failed</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="H1918" t="inlineStr">
